--- a/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
+++ b/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="123">
   <si>
     <t>Summary For B2B, SEZ, DE (4A, 4B, 6B, 6C)</t>
   </si>
@@ -106,9 +106,6 @@
     <t>05-Uttarakhand</t>
   </si>
   <si>
-    <t>06-Haryana</t>
-  </si>
-  <si>
     <t>08-Rajasthan</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>IN-7</t>
   </si>
   <si>
-    <t>LWABOG7260000001</t>
-  </si>
-  <si>
     <t>255724174047155204_1</t>
   </si>
   <si>
@@ -358,46 +352,37 @@
     <t>CANQ1W2600000013</t>
   </si>
   <si>
+    <t>CN-2</t>
+  </si>
+  <si>
+    <t>MFABNVY260000001</t>
+  </si>
+  <si>
+    <t>DAL84U2600000005</t>
+  </si>
+  <si>
+    <t>Sr. No. To</t>
+  </si>
+  <si>
+    <t>6p5kc26244</t>
+  </si>
+  <si>
+    <t>LWABOG7260000005</t>
+  </si>
+  <si>
+    <t>IN-9</t>
+  </si>
+  <si>
+    <t>6p5kc26C98</t>
+  </si>
+  <si>
     <t>LYAA9U7260000001</t>
   </si>
   <si>
-    <t>MFABNVY260000001</t>
-  </si>
-  <si>
-    <t>RAT6SO2600000028</t>
-  </si>
-  <si>
-    <t>DAL84U2600000005</t>
+    <t>RAT6SO2600000034</t>
   </si>
   <si>
     <t>LZAA9B7260000001</t>
-  </si>
-  <si>
-    <t>Sr. No. To</t>
-  </si>
-  <si>
-    <t>6p5kc26244</t>
-  </si>
-  <si>
-    <t>FAWRLX2600000107</t>
-  </si>
-  <si>
-    <t>IN-9</t>
-  </si>
-  <si>
-    <t>LWABOG7260000005</t>
-  </si>
-  <si>
-    <t>6p5kc26C98</t>
-  </si>
-  <si>
-    <t>CANQ1W2600000019</t>
-  </si>
-  <si>
-    <t>MFABNVY260000002</t>
-  </si>
-  <si>
-    <t>RAT6SO2600000034</t>
   </si>
   <si>
     <t>Total Number</t>
@@ -831,12 +816,12 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
@@ -844,15 +829,15 @@
     </row>
     <row r="2" spans="1:5">
       <c r="D2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="D3">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -860,30 +845,30 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>112</v>
@@ -894,16 +879,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -911,13 +896,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -928,13 +913,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -948,13 +933,13 @@
         <v>97</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -962,13 +947,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -979,13 +964,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -996,16 +981,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1013,16 +998,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D13">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1030,16 +1015,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1047,16 +1032,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1067,66 +1052,15 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
         <v>0</v>
       </c>
     </row>
@@ -1200,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1213,7 +1147,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="E2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
@@ -1221,7 +1155,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="E3">
-        <v>16681.17</v>
+        <v>16577.99</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1312,7 +1246,7 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>193.2</v>
+        <v>312.63</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1329,7 +1263,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>312.63</v>
+        <v>2211.99</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1346,7 +1280,7 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>2205.47</v>
+        <v>721.37</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1363,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>721.37</v>
+        <v>303.88</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1380,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <v>303.88</v>
+        <v>1062.14</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1397,7 +1331,7 @@
         <v>3</v>
       </c>
       <c r="E13">
-        <v>1062.14</v>
+        <v>1320.38</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1414,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="E14">
-        <v>1304.84</v>
+        <v>691.27</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1431,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="E15">
-        <v>691.27</v>
+        <v>417.48</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1448,7 +1382,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>401.94</v>
+        <v>436.89</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1465,7 +1399,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>436.89</v>
+        <v>544.65</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1482,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="E18">
-        <v>538.83</v>
+        <v>1549.52</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1499,7 +1433,7 @@
         <v>3</v>
       </c>
       <c r="E19">
-        <v>1549.52</v>
+        <v>1127.18</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1516,7 +1450,7 @@
         <v>3</v>
       </c>
       <c r="E20">
-        <v>1127.18</v>
+        <v>1889.32</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1533,7 +1467,7 @@
         <v>3</v>
       </c>
       <c r="E21">
-        <v>1842.72</v>
+        <v>1178.63</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1550,7 +1484,7 @@
         <v>3</v>
       </c>
       <c r="E22">
-        <v>1178.63</v>
+        <v>1306.77</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1567,26 +1501,9 @@
         <v>3</v>
       </c>
       <c r="E23">
-        <v>1306.77</v>
+        <v>679.61</v>
       </c>
       <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>679.61</v>
-      </c>
-      <c r="F24">
         <v>0</v>
       </c>
     </row>
@@ -1602,7 +1519,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M1" t="s">
         <v>17</v>
@@ -1613,10 +1530,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
@@ -1650,13 +1567,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -1665,10 +1582,10 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
         <v>11</v>
@@ -1695,7 +1612,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
@@ -1703,22 +1620,22 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -1749,19 +1666,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -1770,13 +1687,13 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -1794,7 +1711,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
@@ -1802,22 +1719,22 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -1848,19 +1765,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -1869,13 +1786,13 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -1893,7 +1810,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>17</v>
@@ -1901,22 +1818,22 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
@@ -1947,19 +1864,19 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -1968,13 +1885,13 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
         <v>19</v>
@@ -1992,7 +1909,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
         <v>17</v>
@@ -2000,13 +1917,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2022,36 +1939,36 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +1983,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
         <v>17</v>
@@ -2074,19 +1991,19 @@
     </row>
     <row r="2" spans="1:8">
       <c r="B2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -2097,10 +2014,10 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>16681.17</v>
+        <v>16577.99</v>
       </c>
       <c r="E3">
-        <v>480.09</v>
+        <v>476.99</v>
       </c>
       <c r="F3">
         <v>10.21</v>
@@ -2114,45 +2031,45 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
         <v>90</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>91</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>92</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>93</v>
-      </c>
-      <c r="H4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5">
-        <v>2563.71</v>
+        <v>2653.73</v>
       </c>
       <c r="E5">
-        <v>73.95999999999999</v>
+        <v>76.66</v>
       </c>
       <c r="F5">
         <v>1.5</v>
@@ -2166,19 +2083,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6">
-        <v>1168.91</v>
+        <v>975.71</v>
       </c>
       <c r="E6">
-        <v>35.09</v>
+        <v>29.29</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2192,13 +2109,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7">
         <v>12948.55</v>

--- a/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
+++ b/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
   <si>
     <t>Summary For B2B, SEZ, DE (4A, 4B, 6B, 6C)</t>
   </si>
@@ -337,6 +337,9 @@
     <t>IN-7</t>
   </si>
   <si>
+    <t>LWABOG7260000001</t>
+  </si>
+  <si>
     <t>255724174047155204_1</t>
   </si>
   <si>
@@ -355,34 +358,46 @@
     <t>CN-2</t>
   </si>
   <si>
+    <t>LYAA9U7260000001</t>
+  </si>
+  <si>
     <t>MFABNVY260000001</t>
   </si>
   <si>
+    <t>RAT6SO2600000028</t>
+  </si>
+  <si>
     <t>DAL84U2600000005</t>
   </si>
   <si>
+    <t>LZAA9B7260000001</t>
+  </si>
+  <si>
     <t>Sr. No. To</t>
   </si>
   <si>
     <t>6p5kc26244</t>
   </si>
   <si>
+    <t>FAWRLX2600000107</t>
+  </si>
+  <si>
+    <t>IN-9</t>
+  </si>
+  <si>
     <t>LWABOG7260000005</t>
   </si>
   <si>
-    <t>IN-9</t>
-  </si>
-  <si>
     <t>6p5kc26C98</t>
   </si>
   <si>
-    <t>LYAA9U7260000001</t>
+    <t>CANQ1W2600000019</t>
+  </si>
+  <si>
+    <t>MFABNVY260000002</t>
   </si>
   <si>
     <t>RAT6SO2600000034</t>
-  </si>
-  <si>
-    <t>LZAA9B7260000001</t>
   </si>
   <si>
     <t>Total Number</t>
@@ -816,7 +831,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -829,10 +844,10 @@
     </row>
     <row r="2" spans="1:5">
       <c r="D2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -851,13 +866,13 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -868,7 +883,7 @@
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D5">
         <v>112</v>
@@ -885,10 +900,10 @@
         <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -919,7 +934,7 @@
         <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -930,16 +945,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -987,10 +1002,10 @@
         <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1004,10 +1019,10 @@
         <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1021,10 +1036,10 @@
         <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1038,10 +1053,10 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1049,18 +1064,86 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
         <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
         <v>0</v>
       </c>
     </row>

--- a/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
+++ b/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
@@ -2939,7 +2939,7 @@
         <v>76.66</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>1.49</v>

--- a/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
+++ b/storage/exports/4/07TCRPS8655B1ZK/032026/gstr1.xlsx
@@ -1,10 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="b2b,sez,de" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,294 +17,556 @@
     <sheet name="eco" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="docs" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'b2b,sez,de'!$A$4:$M$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'b2b,sez,de'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'b2b,sez,de'!$A$1:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'b2cl'!$A$4:$I$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'b2cl'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'b2cl'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'b2cs'!$A$4:$G$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'b2cs'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'b2cs'!$A$1:$G$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'cdnr'!$A$4:$M$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'cdnr'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'cdnr'!$A$1:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'hsn'!$A$4:$K$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'hsn'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'hsn'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hsn(b2b)'!$A$4:$K$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'hsn(b2b)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'hsn(b2b)'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'hsn(b2c)'!$A$4:$K$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'hsn(b2c)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'hsn(b2c)'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'exemp'!$A$4:$D$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'exemp'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'exemp'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'eco'!$A$4:$H$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'eco'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'eco'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'docs'!$A$4:$E$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'docs'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'docs'!$A$1:$E$12</definedName>
-  </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" fullCalcOnLoad="1" calcCompleted="0"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;[Red]0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <strike val="0"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <strike val="0"/>
+      <color rgb="FF0A0101"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <strike val="0"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="000F172A"/>
-      <sz val="10"/>
+      <strike val="0"/>
+      <color rgb="FF0563C1"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0010244D"/>
+        <fgColor rgb="FF0070C0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6FA"/>
+        <fgColor rgb="FFF7CAAC"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4D6"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAFBFD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001746A2"/>
+        <fgColor rgb="FFF7CAAC"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="0094A3B8"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
+      <right style="medium">
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="0094A3B8"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
-        <color rgb="0094A3B8"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="0094A3B8"/>
-      </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="0094A3B8"/>
-      </right>
-      <top style="medium">
-        <color rgb="0094A3B8"/>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="0094A3B8"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="82">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1">
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="2" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="7" borderId="2" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="12">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="bottom"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="1" hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="11">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="gst_title" xfId="1" hidden="0"/>
-    <cellStyle name="gst_summary_label" xfId="2" hidden="0"/>
-    <cellStyle name="gst_summary_value" xfId="3" hidden="0"/>
-    <cellStyle name="gst_header" xfId="4" hidden="0"/>
-    <cellStyle name="gst_text" xfId="5" hidden="0"/>
-    <cellStyle name="gst_text_alt" xfId="6" hidden="0"/>
-    <cellStyle name="gst_number" xfId="7" hidden="0"/>
-    <cellStyle name="gst_number_alt" xfId="8" hidden="0"/>
-    <cellStyle name="gst_integer" xfId="9" hidden="0"/>
-    <cellStyle name="gst_help" xfId="10" hidden="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -452,6 +713,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -486,6 +748,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -664,183 +927,191 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="40.85546875" customWidth="1" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" min="2" max="2"/>
+    <col width="15.28515625" customWidth="1" min="3" max="3"/>
+    <col width="11.28515625" customWidth="1" min="4" max="4"/>
+    <col width="19.5703125" customWidth="1" min="5" max="5"/>
+    <col width="14.85546875" customWidth="1" min="6" max="6"/>
+    <col width="14.85546875" customWidth="1" min="7" max="7"/>
+    <col width="12.28515625" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.28515625" customWidth="1" min="10" max="10"/>
+    <col width="5.85546875" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12.42578125" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Summary For B2B, SEZ, DE (4A, 4B, 6B, 6C)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="5" t="n"/>
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>No. of Recipients</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>No. of Invoices</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Total Invoice Value</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="9" t="n"/>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>Total Taxable Value</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="81">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>GSTIN/UIN of Recipient</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Receiver Name</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Invoice date</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Invoice Value</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Place Of Supply</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Reverse Charge</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>Applicable % of Tax Rate</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>Invoice Type</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>E-Commerce GSTIN</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="M1" location="B2B"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -848,277 +1119,285 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="50.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.140625" customWidth="1" min="2" max="2"/>
+    <col width="10.42578125" customWidth="1" min="3" max="3"/>
+    <col width="14.5703125" customWidth="1" min="4" max="4"/>
+    <col width="15.85546875" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28.5" customHeight="1" s="81">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Summary of documents issued during the tax period (13)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="3" t="n"/>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="B1" s="75" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="44" t="n"/>
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="76" t="n"/>
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Total Number</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Total Cancelled</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="n">
+    <row r="3">
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="77" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>Nature of Document</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>Sr. No. From</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="79" t="inlineStr">
         <is>
           <t>Sr. No. To</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Total Number</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Invoices for outward supply</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>6p5kc26133</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>6p5kc26244</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="0" t="n">
         <v>112</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>6p5kc26C68</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>6p5kc27C1</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>Invoices for outward supply</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>IN-5</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>IN-9</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>Invoices for outward supply</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>FAWRLX2600000080</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>LWABOG7260000005</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>MFABNVY260000001</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>RAT6SO2600000034</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D9" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Invoices for outward supply</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>IN-5</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>IN-9</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Invoices for outward supply</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>FAWRLX2600000080</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>LWABOG7260000005</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>CANQ1W2600000013</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>LYAA9U7260000001</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Debit Note</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>DAL84U2600000005</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>LZAA9B7260000001</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>CN-2</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>CN-2</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Debit Note</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>DAL84U2600000005</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>LZAA9B7260000001</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E12"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="E1" location="DOCS"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1126,127 +1405,135 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22.7109375" customWidth="1" min="1" max="1"/>
+    <col width="11.28515625" customWidth="1" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" min="3" max="3"/>
+    <col width="16.140625" customWidth="1" min="4" max="4"/>
+    <col width="16.85546875" customWidth="1" min="5" max="5"/>
+    <col width="6.85546875" customWidth="1" min="6" max="6"/>
+    <col width="14.140625" customWidth="1" min="7" max="7"/>
+    <col width="13.5703125" customWidth="1" min="8" max="8"/>
+    <col width="19.28515625" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Summary For B2CL(5)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="3" t="n"/>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="49" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="44" t="n"/>
+      <c r="G1" s="49" t="n"/>
+      <c r="H1" s="70" t="n"/>
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>No. of Invoices</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="71" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="71" t="n"/>
+      <c r="H2" s="72" t="n"/>
+      <c r="I2" s="10" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="73" t="n"/>
+      <c r="I3" s="13" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="81">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Invoice date</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Invoice Value</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Place Of Supply</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Applicable % of Tax Rate</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>E-Commerce GSTIN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="I1" location="b2cl"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1254,617 +1541,603 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22.42578125" customWidth="1" min="1" max="1"/>
+    <col width="14.85546875" customWidth="1" min="2" max="2"/>
+    <col width="14.7109375" customWidth="1" min="3" max="3"/>
+    <col width="5.85546875" customWidth="1" min="4" max="4"/>
+    <col width="20.5703125" customWidth="1" min="5" max="5"/>
+    <col width="12.42578125" customWidth="1" min="6" max="6"/>
+    <col width="19.28515625" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Summary For B2CS(7)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="21" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Total Taxable  Value</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="G2" s="21" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="81">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Place Of Supply</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Applicable % of Tax Rate</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>E-Commerce GSTIN</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>37-Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="9" t="n">
+      <c r="C5" s="0" t="n"/>
+      <c r="D5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="0" t="n">
         <v>1306.79</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n"/>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>18-Assam</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="9" t="n">
+      <c r="C6" s="0" t="n"/>
+      <c r="D6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11" t="n"/>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>10-Bihar</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="9" t="n">
+      <c r="C7" s="0" t="n"/>
+      <c r="D7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="0" t="n">
         <v>721.36</v>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n"/>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>04-Chandigarh</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="9" t="n">
+      <c r="C8" s="0" t="n"/>
+      <c r="D8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="11" t="n"/>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>22-Chhattisgarh</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="9" t="n">
+      <c r="C9" s="0" t="n"/>
+      <c r="D9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="0" t="n">
         <v>691.26</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8" t="n"/>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>07-Delhi</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="9" t="n">
+      <c r="C10" s="0" t="n"/>
+      <c r="D10" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="0" t="n">
         <v>679.6</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n"/>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>24-Gujarat</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9" t="n">
+      <c r="C11" s="0" t="n"/>
+      <c r="D11" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="0" t="n">
         <v>436.89</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="n"/>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>06-Haryana</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="9" t="n">
+      <c r="C12" s="0" t="n"/>
+      <c r="D12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="11" t="n"/>
+      <c r="E12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>20-Jharkhand</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="9" t="n">
+      <c r="C13" s="0" t="n"/>
+      <c r="D13" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="n"/>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>29-Karnataka</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="9" t="n">
+      <c r="C14" s="0" t="n"/>
+      <c r="D14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="0" t="n">
         <v>1549.51</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="n"/>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>32-Kerala</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="9" t="n">
+      <c r="C15" s="0" t="n"/>
+      <c r="D15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="0" t="n">
         <v>1127.19</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="n"/>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>23-Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="9" t="n">
+      <c r="C16" s="0" t="n"/>
+      <c r="D16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="0" t="n">
         <v>417.48</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>27-Maharashtra</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="9" t="n">
+      <c r="C17" s="0" t="n"/>
+      <c r="D17" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="0" t="n">
         <v>544.66</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="n"/>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>21-Odisha</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="9" t="n">
+      <c r="C18" s="0" t="n"/>
+      <c r="D18" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="0" t="n">
         <v>1320.38</v>
       </c>
-      <c r="F18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>03-Punjab</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="9" t="n">
+      <c r="C19" s="0" t="n"/>
+      <c r="D19" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="0" t="n">
         <v>672.83</v>
       </c>
-      <c r="F19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="8" t="n"/>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>08-Rajasthan</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="9" t="n">
+      <c r="C20" s="0" t="n"/>
+      <c r="D20" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="0" t="n">
         <v>312.62</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="11" t="n"/>
+      <c r="F20" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>33-Tamil Nadu</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="9" t="n">
+      <c r="C21" s="0" t="n"/>
+      <c r="D21" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="0" t="n">
         <v>1889.31</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="8" t="n"/>
+      <c r="F21" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>36-Telangana</t>
         </is>
       </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="9" t="n">
+      <c r="C22" s="0" t="n"/>
+      <c r="D22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="0" t="n">
         <v>1178.64</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>16-Tripura</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9" t="n">
+      <c r="C23" s="0" t="n"/>
+      <c r="D23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="0" t="n">
         <v>303.88</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="8" t="n"/>
+      <c r="F23" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>09-Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="9" t="n">
+      <c r="C24" s="0" t="n"/>
+      <c r="D24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="0" t="n">
         <v>2211.99</v>
       </c>
-      <c r="F24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11" t="n"/>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>05-Uttarakhand</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="9" t="n">
+      <c r="C25" s="0" t="n"/>
+      <c r="D25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="0" t="n">
         <v>151.46</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="8" t="n"/>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>OE</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>19-West Bengal</t>
         </is>
       </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="9" t="n">
+      <c r="C26" s="0" t="n"/>
+      <c r="D26" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="0" t="n">
         <v>1062.14</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11" t="n"/>
+      <c r="F26" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G26"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="G1" location="B2CS"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1872,183 +2145,191 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="24.85546875" customWidth="1" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" min="3" max="3"/>
+    <col width="9.85546875" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14.85546875" customWidth="1" min="6" max="6"/>
+    <col width="14.85546875" customWidth="1" min="7" max="7"/>
+    <col width="16.28515625" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12.7109375" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12.42578125" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>Summary For CDNR(9B)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="43" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="44" t="n"/>
+      <c r="L1" s="44" t="n"/>
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>No. of Recipients</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>No. of Notes</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Total Note Value</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="9" t="n"/>
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>Total Taxable Value</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="81">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>GSTIN/UIN of Recipient</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>Receiver Name</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>Note Number</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>Note Date</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="46" t="inlineStr">
         <is>
           <t>Note Type</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Place Of Supply</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Reverse Charge</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Note Supply Type</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="47" t="inlineStr">
         <is>
           <t>Note Value</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Applicable % of Tax Rate</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="47" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="47" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M4" s="47" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="M1" location="CDNR"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2056,177 +2337,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22.5703125" customWidth="1" min="1" max="1"/>
+    <col width="10.5703125" customWidth="1" min="2" max="2"/>
+    <col width="6.28515625" customWidth="1" min="3" max="3"/>
+    <col width="13.140625" customWidth="1" min="4" max="4"/>
+    <col width="11.7109375" customWidth="1" min="5" max="5"/>
+    <col width="6.140625" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" min="9" max="9"/>
+    <col width="20.140625" customWidth="1" min="10" max="10"/>
+    <col width="12.42578125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="81">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Summary For HSN(12)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="27" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>No. of HSN</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>Total Taxable Value</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>Total Integrated Tax</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>Total Central Tax</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="32" t="inlineStr">
         <is>
           <t>Total State/UT Tax</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="33" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="37" t="n"/>
+      <c r="E3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="37" t="n"/>
+      <c r="G3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>HSN</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>UQC</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Total Quantity</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Integrated Tax Amount</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Central Tax Amount</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>State/UT Tax Amount</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="K1" location="HSN"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2234,177 +2523,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22.5703125" customWidth="1" min="1" max="1"/>
+    <col width="10.5703125" customWidth="1" min="2" max="2"/>
+    <col width="6.28515625" customWidth="1" min="3" max="3"/>
+    <col width="13.140625" customWidth="1" min="4" max="4"/>
+    <col width="11.7109375" customWidth="1" min="5" max="5"/>
+    <col width="6.140625" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" min="9" max="9"/>
+    <col width="20.140625" customWidth="1" min="10" max="10"/>
+    <col width="12.42578125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="81">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Summary For HSN(12)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="27" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>No. of HSN</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>Total Taxable Value</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>Total Integrated Tax</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>Total Central Tax</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="32" t="inlineStr">
         <is>
           <t>Total State/UT Tax</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="33" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="37" t="n"/>
+      <c r="E3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="37" t="n"/>
+      <c r="G3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>HSN</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>UQC</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Total Quantity</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Integrated Tax Amount</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Central Tax Amount</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>State/UT Tax Amount</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="K1" location="HSN"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2412,177 +2709,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22.5703125" customWidth="1" min="1" max="1"/>
+    <col width="10.5703125" customWidth="1" min="2" max="2"/>
+    <col width="6.42578125" customWidth="1" min="3" max="3"/>
+    <col width="13.140625" customWidth="1" min="4" max="4"/>
+    <col width="11.7109375" customWidth="1" min="5" max="5"/>
+    <col width="6.140625" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" min="9" max="9"/>
+    <col width="20.140625" customWidth="1" min="10" max="10"/>
+    <col width="12.42578125" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="81">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Summary For HSN(12)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="27" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="81">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>No. of HSN</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="B2" s="29" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>Total Taxable Value</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>Total Integrated Tax</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>Total Central Tax</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="32" t="inlineStr">
         <is>
           <t>Total State/UT Tax</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="33" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="37" t="n"/>
+      <c r="E3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="37" t="n"/>
+      <c r="G3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>HSN</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>UQC</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Total Quantity</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>Total Value</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>Taxable Value</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Integrated Tax Amount</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Central Tax Amount</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>State/UT Tax Amount</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="41" t="inlineStr">
         <is>
           <t>Cess Amount</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K4"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <hyperlinks>
+    <hyperlink ref="K1" location="HSN"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2590,130 +2895,176 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="38.140625" customWidth="1" min="1" max="1"/>
+    <col width="24.140625" customWidth="1" min="2" max="2"/>
+    <col width="24.85546875" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28.5" customHeight="1" s="81">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Summary For Nil rated, exempted and non GST outward supplies (8)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="n"/>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="B1" s="49" t="n"/>
+      <c r="C1" s="44" t="n"/>
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Total Nil Rated Supplies</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>Total Exempted Supplies</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Total Non-GST Supplies</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="81">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Nil Rated Supplies</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="52" t="inlineStr">
         <is>
           <t>Exempted(other than nil rated/non GST supply)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Non-GST Supplies</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Inter-State supplies to registered persons</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="B5" s="55" t="n"/>
+      <c r="C5" s="55" t="n"/>
+      <c r="D5" s="55" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>Intra-State supplies to registered persons</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
+      <c r="B6" s="55" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="55" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Inter-State supplies to unregistered persons</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>Intra-State supplies to unregistered persons</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D8"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <dataValidations count="12">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="D8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="Negative value not allowed. Please enter positive value." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D1" location="'Help Instruction'!B233"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2721,239 +3072,367 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelRow="0"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="39.5703125" customWidth="1" min="1" max="1"/>
+    <col width="31.42578125" customWidth="1" min="2" max="2"/>
+    <col width="27.7109375" customWidth="1" min="3" max="3"/>
+    <col width="27.85546875" customWidth="1" min="4" max="4"/>
+    <col width="21.140625" customWidth="1" min="5" max="5"/>
+    <col width="18.85546875" customWidth="1" min="6" max="6"/>
+    <col width="20.28515625" customWidth="1" min="7" max="7"/>
+    <col width="12.7109375" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="81">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>Summary For Supplies through ECO-14</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="3" t="n"/>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="B1" s="56" t="n"/>
+      <c r="C1" s="57" t="n"/>
+      <c r="D1" s="58" t="n"/>
+      <c r="E1" s="58" t="n"/>
+      <c r="F1" s="58" t="n"/>
+      <c r="G1" s="58" t="n"/>
+      <c r="H1" s="59" t="inlineStr">
         <is>
           <t>HELP</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="31" customHeight="1">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="5" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="81">
+      <c r="A2" s="60" t="n"/>
+      <c r="B2" s="60" t="inlineStr">
         <is>
           <t>No. of E-Commerce Operator</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="C2" s="60" t="n"/>
+      <c r="D2" s="60" t="inlineStr">
         <is>
           <t>Total Net Value of Supplies</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="60" t="inlineStr">
         <is>
           <t>Total Integrated Tax</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">Total Central Tax </t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">Total State/UT Tax </t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="60" t="inlineStr">
         <is>
           <t>Total Cess</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="81">
+      <c r="A3" s="67" t="n"/>
+      <c r="B3" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" s="81">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>Nature of Supply</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>GSTIN of E-Commerce Operator</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>E-Commerce Operator Name</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>Net value of supplies</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>Integrated tax</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="62" t="inlineStr">
         <is>
           <t>Central tax</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="62" t="inlineStr">
         <is>
           <t>State/UT tax</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="62" t="inlineStr">
         <is>
           <t>Cess</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1" s="81">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Liable to collect tax u/s 52(TCS)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>07AARCM9332R1CQ</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>meesho</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="55" t="n">
         <v>12948.55</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="55" t="n">
         <v>371.04</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="55" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="55" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="H5" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="81">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Liable to collect tax u/s 52(TCS)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="65" t="inlineStr">
         <is>
           <t>07AAICA3918J1CV</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>amazon</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="55" t="n">
         <v>975.71</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="55" t="n">
         <v>29.29</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="F6" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="81">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>Liable to collect tax u/s 52(TCS)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>07AACCF0683K1CU</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="55" t="n">
         <v>2653.73</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="55" t="n">
         <v>76.66</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="55" t="n">
         <v>1.49</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="55" t="n">
         <v>1.49</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="H7" s="55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="81"/>
   </sheetData>
-  <autoFilter ref="A4:H7"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <dataValidations count="39">
+    <dataValidation sqref="D1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="D8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="E8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-9.99999999999999E+21</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="GSTIN should be 15 characters. Please Enter valid GSTIN." type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="GSTIN should be 15 characters. Please Enter valid GSTIN." type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="GSTIN should be 15 characters. Please Enter valid GSTIN." type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="GSTIN should be 15 characters. Please Enter valid GSTIN." type="textLength" operator="equal">
+      <formula1>15</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H1" location="'Help Instruction'!B256"/>
+  </hyperlinks>
+  <printOptions gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="default" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>